--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/contdid_rf_continuous.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/contdid_rf_continuous.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">Pre</t>
   </si>
   <si>
-    <t xml:space="preserve">Post</t>
+    <t xml:space="preserve">*</t>
   </si>
   <si>
-    <t xml:space="preserve">*</t>
+    <t xml:space="preserve">Post</t>
   </si>
 </sst>
 </file>
@@ -407,7 +407,7 @@
     <col min="5" max="5" width="13.67625" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.4975" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="13.67625" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.67625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.4975" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="5.425" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
@@ -515,13 +515,13 @@
         <v>4460.2376</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2972.2205</v>
+        <v>3556.4069</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-96491.8133</v>
+        <v>-3183.4086</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>105412.2885</v>
+        <v>12103.8838</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -543,13 +543,13 @@
         <v>-13084.8487</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>4717.3418</v>
+        <v>11245.8075</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-173310.2819</v>
+        <v>-37255.0228</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>147140.5845</v>
+        <v>11085.3253</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -571,16 +571,16 @@
         <v>-2974.0337</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>685.6586</v>
+        <v>1284.3452</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-26262.5614</v>
+        <v>-5734.4267</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>20314.494</v>
+        <v>-213.6407</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>11</v>
@@ -599,13 +599,13 @@
         <v>-13127.8644</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>9418.9655</v>
+        <v>12011.9272</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-333044.8654</v>
+        <v>-38944.6296</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>306789.1366</v>
+        <v>12688.9008</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -627,16 +627,16 @@
         <v>-25341.6176</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>6065.3853</v>
+        <v>11588.7396</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-231353.6135</v>
+        <v>-50248.8421</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>180670.3784</v>
+        <v>-434.393</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>11</v>
@@ -655,13 +655,13 @@
         <v>-8116.7853</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2966.3692</v>
+        <v>8721.0549</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-108870.0945</v>
+        <v>-26860.6074</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>92636.524</v>
+        <v>10627.0368</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -683,13 +683,13 @@
         <v>18094.5521</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>7058.1345</v>
+        <v>11346.9204</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-221636.3645</v>
+        <v>-6292.94</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>257825.4687</v>
+        <v>42482.0443</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -711,16 +711,16 @@
         <v>-10779.9425</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>9801.0949</v>
+        <v>4439.3132</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-343676.0423</v>
+        <v>-20321.1847</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>322116.1572</v>
+        <v>-1238.7003</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>11</v>
@@ -739,13 +739,13 @@
         <v>5438.0581</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>987.4638</v>
+        <v>7123.9565</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-28101.3432</v>
+        <v>-9873.183</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>38977.4593</v>
+        <v>20749.2991</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -767,13 +767,13 @@
         <v>-825.4116</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>644.9385</v>
+        <v>3260.9529</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-22730.8733</v>
+        <v>-7834.05</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>21080.0501</v>
+        <v>6183.2268</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -795,16 +795,16 @@
         <v>16822.9325</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>4260.064</v>
+        <v>7717.975</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-127870.974</v>
+        <v>234.9908</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>161516.8391</v>
+        <v>33410.8743</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>11</v>
@@ -823,13 +823,13 @@
         <v>8592.9365</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>12252.5165</v>
+        <v>11898.036</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-407566.1765</v>
+        <v>-16979.0468</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>424752.0496</v>
+        <v>34164.9198</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -851,13 +851,13 @@
         <v>-1005.8523</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1327.7932</v>
+        <v>4658.5732</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-46104.6089</v>
+        <v>-11018.3413</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>44092.9043</v>
+        <v>9006.6367</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -879,16 +879,16 @@
         <v>-14986.6735</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>9860.612</v>
+        <v>5397.7309</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-349904.2832</v>
+        <v>-26587.8054</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>319930.9362</v>
+        <v>-3385.5415</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>11</v>
@@ -907,13 +907,13 @@
         <v>2944.083</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>4253.8576</v>
+        <v>5372.5223</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-141539.0196</v>
+        <v>-8602.869</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>147427.1856</v>
+        <v>14491.035</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -935,13 +935,13 @@
         <v>-11654.4675</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>5255.6867</v>
+        <v>7445.8491</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-190164.8935</v>
+        <v>-27657.5396</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>166855.9585</v>
+        <v>4348.6047</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -963,13 +963,13 @@
         <v>-11331.6331</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>6306.5898</v>
+        <v>6529.4902</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-225536.1866</v>
+        <v>-25365.2109</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>202872.9204</v>
+        <v>2701.9447</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -991,13 +991,13 @@
         <v>5368.4507</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>2483.4716</v>
+        <v>5000.0833</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-78983.1471</v>
+        <v>-5378.0329</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>89720.0484</v>
+        <v>16114.9342</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1019,13 +1019,13 @@
         <v>18540.2958</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>12095.2341</v>
+        <v>10453.7332</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-392276.6902</v>
+        <v>-3927.5039</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>429357.2817</v>
+        <v>41008.0955</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1047,19 +1047,19 @@
         <v>-1165.8499</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>1770.018</v>
+        <v>3509.9714</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-61284.8555</v>
+        <v>-8709.6941</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>58953.1556</v>
+        <v>6377.9942</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1075,19 +1075,19 @@
         <v>6150.1045</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>902.443</v>
+        <v>4734.6951</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-24501.5472</v>
+        <v>-4025.9904</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>36801.7563</v>
+        <v>16326.1995</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1103,19 +1103,19 @@
         <v>11893.6676</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>517.5522</v>
+        <v>9246.3943</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-5685.0951</v>
+        <v>-7979.2458</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>29472.4303</v>
+        <v>31766.5811</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1131,19 +1131,19 @@
         <v>20537.4161</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4761.9448</v>
+        <v>10268.4245</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-141202.968</v>
+        <v>-1532.1069</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>182277.8003</v>
+        <v>42606.9392</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1159,19 +1159,19 @@
         <v>25309.1661</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>1782.3577</v>
+        <v>12588.1924</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>-35228.9597</v>
+        <v>-1746.1433</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>85847.2919</v>
+        <v>52364.4755</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1187,19 +1187,19 @@
         <v>24631.4646</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>10933.3513</v>
+        <v>6130.9526</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>-346721.9469</v>
+        <v>11454.448</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>395984.8761</v>
+        <v>37808.4812</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1215,19 +1215,19 @@
         <v>9385.1156</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>5889.5233</v>
+        <v>8210.3186</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>-190653.6941</v>
+        <v>-8261.001</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>209423.9253</v>
+        <v>27031.2323</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1243,19 +1243,19 @@
         <v>11898.4126</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>10013.7508</v>
+        <v>9713.0591</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>-328220.5877</v>
+        <v>-8977.4853</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>352017.4129</v>
+        <v>32774.3104</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1271,19 +1271,19 @@
         <v>-1403.094</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>12634.8324</v>
+        <v>7395.5733</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-430547.6415</v>
+        <v>-17298.1105</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>427741.4534</v>
+        <v>14491.9224</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1299,19 +1299,19 @@
         <v>-9668.8905</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>6525.2223</v>
+        <v>6750.9653</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>-231299.3399</v>
+        <v>-24178.4761</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>211961.5589</v>
+        <v>4840.6951</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1327,19 +1327,19 @@
         <v>-6903.446</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>3615.6372</v>
+        <v>4376.07</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-129709.2693</v>
+        <v>-16308.762</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>115902.3772</v>
+        <v>2501.8699</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1355,19 +1355,19 @@
         <v>7076.2835</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>7074.1328</v>
+        <v>4114.1312</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>-233198.0167</v>
+        <v>-1766.0577</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>247350.5837</v>
+        <v>15918.6248</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1383,19 +1383,19 @@
         <v>4734.9247</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>3827.139</v>
+        <v>3001.0446</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>-125254.5986</v>
+        <v>-1715.1031</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>134724.4481</v>
+        <v>11184.9525</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1411,19 +1411,19 @@
         <v>6052.8997</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>5003.8896</v>
+        <v>4962.403</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>-163905.1855</v>
+        <v>-4612.599</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>176010.9849</v>
+        <v>16718.3984</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1439,19 +1439,19 @@
         <v>16122.6836</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>12208.5454</v>
+        <v>4865.617</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>-398542.9419</v>
+        <v>5665.2033</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>430788.3091</v>
+        <v>26580.1638</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -1467,19 +1467,19 @@
         <v>21750.0879</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>19355.2389</v>
+        <v>11461.6004</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>-635654.3778</v>
+        <v>-2883.8814</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>679154.5535</v>
+        <v>46384.0571</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -1495,19 +1495,19 @@
         <v>21327.1207</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>12214.2742</v>
+        <v>8984.1347</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>-393533.0849</v>
+        <v>2017.8716</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>436187.3263</v>
+        <v>40636.3699</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -1523,19 +1523,19 @@
         <v>19108.9356</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>11430.6124</v>
+        <v>13519.5334</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>-369134.0447</v>
+        <v>-9948.0685</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>407351.9159</v>
+        <v>48165.9398</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -1551,19 +1551,19 @@
         <v>17103.9995</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>10033.8418</v>
+        <v>11000.1215</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>-323697.3951</v>
+        <v>-6538.1313</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>357905.3941</v>
+        <v>40746.1303</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -1579,19 +1579,19 @@
         <v>9113.9721</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>9510.9004</v>
+        <v>8236.5464</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>-313925.6177</v>
+        <v>-8588.5148</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>332153.5618</v>
+        <v>26816.4589</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -1607,19 +1607,19 @@
         <v>1201.9937</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>2033.6956</v>
+        <v>5780.1169</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>-67872.8751</v>
+        <v>-11220.9854</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>70276.8626</v>
+        <v>13624.9728</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -1635,19 +1635,19 @@
         <v>-4786.1351</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>6462.4371</v>
+        <v>5491.5895</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>-224284.0709</v>
+        <v>-16588.9936</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>214711.8007</v>
+        <v>7016.7234</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -1663,19 +1663,19 @@
         <v>-15312.8459</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>10204.8419</v>
+        <v>7224.6792</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>-361922.2922</v>
+        <v>-30840.5662</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>331296.6005</v>
+        <v>214.8745</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -1691,19 +1691,19 @@
         <v>9614.093</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>2325.9535</v>
+        <v>3983.1688</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>-69387.3704</v>
+        <v>1053.2241</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>88615.5564</v>
+        <v>18174.9618</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -1719,19 +1719,19 @@
         <v>2857.4706</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>1099.7867</v>
+        <v>2492.8148</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>-34497.0006</v>
+        <v>-2500.2388</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>40211.9418</v>
+        <v>8215.18</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -1747,19 +1747,19 @@
         <v>749.733</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>3497.7861</v>
+        <v>2476.005</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>-118053.2537</v>
+        <v>-4571.8476</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>119552.7197</v>
+        <v>6071.3136</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -1775,19 +1775,19 @@
         <v>14584.0226</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>6157.3555</v>
+        <v>8616.2919</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>-194551.7577</v>
+        <v>-3934.6364</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>223719.803</v>
+        <v>33102.6816</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -1803,19 +1803,19 @@
         <v>18630.9359</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>7191.999</v>
+        <v>9437.3386</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-225646.7141</v>
+        <v>-1652.3668</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>262908.586</v>
+        <v>38914.2386</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -1831,19 +1831,19 @@
         <v>19877.9407</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>195.6189</v>
+        <v>12211.0348</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>13233.7077</v>
+        <v>-6366.7587</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>26522.1737</v>
+        <v>46122.6401</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -1859,19 +1859,19 @@
         <v>21133.8286</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>2805.6567</v>
+        <v>18106.7187</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-74160.8478</v>
+        <v>-17782.2335</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>116428.505</v>
+        <v>60049.8908</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -1887,19 +1887,19 @@
         <v>15433.2585</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>11021.1786</v>
+        <v>9294.1839</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>-358903.2236</v>
+        <v>-4542.3674</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>389769.7405</v>
+        <v>35408.8844</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -1915,19 +1915,19 @@
         <v>12687.8503</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>7382.2637</v>
+        <v>11178.1835</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-238052.1765</v>
+        <v>-11336.9821</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>263427.8771</v>
+        <v>36712.6827</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -1943,19 +1943,19 @@
         <v>321.3628</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>3250.0979</v>
+        <v>5576.5109</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>-110068.8457</v>
+        <v>-11664.014</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>110711.5713</v>
+        <v>12306.7396</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -1971,19 +1971,19 @@
         <v>-9454.898</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>1204.9557</v>
+        <v>7093.6672</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>-50381.4533</v>
+        <v>-24701.0394</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>31471.6572</v>
+        <v>5791.2434</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -1999,19 +1999,19 @@
         <v>-14910.1049</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>8307.9828</v>
+        <v>6980.1588</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>-297092.3631</v>
+        <v>-29912.2871</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>267272.1532</v>
+        <v>92.0772</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2027,19 +2027,19 @@
         <v>10658.4745</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>2795.7543</v>
+        <v>7260.6462</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>-84299.866</v>
+        <v>-4946.5483</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>105616.8149</v>
+        <v>26263.4973</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2055,19 +2055,19 @@
         <v>-1533.6215</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>2421.9752</v>
+        <v>2356.5823</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>-83796.4822</v>
+        <v>-6598.5316</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>80729.2392</v>
+        <v>3531.2886</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2083,19 +2083,19 @@
         <v>1409.3099</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>1698.3749</v>
+        <v>3155.5284</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>-56276.3255</v>
+        <v>-5372.7439</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>59094.9453</v>
+        <v>8191.3636</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2111,19 +2111,19 @@
         <v>13765.365</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>11982.7117</v>
+        <v>8917.6273</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>-393229.7777</v>
+        <v>-5400.9424</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>420760.5077</v>
+        <v>32931.6724</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2139,19 +2139,19 @@
         <v>14663.4141</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>3331.8455</v>
+        <v>7122.8276</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>-98503.367</v>
+        <v>-645.4006</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>127830.1951</v>
+        <v>29972.2288</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2167,19 +2167,19 @@
         <v>20307.5878</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>5306.8114</v>
+        <v>12779.7592</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>-159939.2984</v>
+        <v>-7159.4486</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>200554.474</v>
+        <v>47774.6242</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2195,19 +2195,19 @@
         <v>21029.2409</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>986.4164</v>
+        <v>12508.4194</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>-12474.5843</v>
+        <v>-5854.6155</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>54533.0662</v>
+        <v>47913.0974</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2223,19 +2223,19 @@
         <v>7818.4963</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>6477.7212</v>
+        <v>5567.1145</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>-212198.5695</v>
+        <v>-4146.685</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>227835.5621</v>
+        <v>19783.6776</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
